--- a/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
+++ b/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Q3-Q4 Charter Model" sheetId="1" r:id="rId1"/>
+    <sheet name="Harbor_Manifest_2026" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -13,99 +13,100 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Berth #</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Projected Trips</t>
+          <t>Vessel Name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Gross Charter ($)</t>
+          <t>LOA (ft)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Dock &amp; Fuel ($)</t>
+          <t>Beam</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Crew ($)</t>
+          <t>Slip Fee / Mo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Net Operating ($)</t>
+          <t>Commercial Permit #</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Expiration Date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Slip K-14</t>
         </is>
       </c>
-      <c r="B2">
-        <v>34</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Makani Catamaran</t>
+        </is>
       </c>
       <c r="C2">
-        <v>48200</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>9400</v>
+        <v>22.5</v>
       </c>
       <c r="E2">
-        <v>11900</v>
+        <v>940.0</v>
       </c>
-      <c r="F2">
-        <v>26900</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DOCARE-OAHU-2026-44</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>Slip K-15</t>
         </is>
       </c>
-      <c r="B3">
-        <v>38</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hoku Sportfisher</t>
+        </is>
       </c>
       <c r="C3">
-        <v>54600</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>10200</v>
+        <v>12.0</v>
       </c>
       <c r="E3">
-        <v>13300</v>
+        <v>720.0</v>
       </c>
-      <c r="F3">
-        <v>31100</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>DOCARE-OAHU-2026-45</t>
         </is>
       </c>
-      <c r="B4">
-        <v>42</v>
-      </c>
-      <c r="C4">
-        <v>61400</v>
-      </c>
-      <c r="D4">
-        <v>11500</v>
-      </c>
-      <c r="E4">
-        <v>14700</v>
-      </c>
-      <c r="F4">
-        <v>35200</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
+++ b/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
@@ -1,114 +1,599 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Harbor_Manifest_2026" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harbor_Manifest_2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="3">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
+  </fonts>
+  <fills count="5">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Berth #</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Vessel Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>LOA (ft)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Beam</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Slip Fee / Mo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Commercial Permit #</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Expiration Date</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Slip K-14</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Makani Catamaran</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="C2" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="E2">
-        <v>940.0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="5" t="n">
+        <v>940</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>DOCARE-OAHU-2026-44</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>2027-06-30</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Slip K-15</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Hoku Sportfisher</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="D3">
-        <v>12.0</v>
-      </c>
-      <c r="E3">
-        <v>720.0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="D3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>720</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>DOCARE-OAHU-2026-45</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2027-06-30</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
+++ b/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,9 +99,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -110,9 +107,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -482,114 +476,2112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Berth #</t>
+          <t>Slip ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Harbor Location</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Berth Berth Tier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Vessel Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LOA (ft)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Beam</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Slip Fee / Mo</t>
+          <t>Length Overall (LOA)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Commercial Permit #</t>
+          <t>Beam (ft)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Expiration Date</t>
+          <t>Draft (ft)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly Berth Fee USD</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Electric Metered Fee</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Commercial Landing Permit</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Insurance Exp Date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Owner / Management Entity</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Slip K-14</t>
+          <t>BERTH-KW-101</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Makani Catamaran</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>940</v>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Pearl</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>DOCARE-OAHU-2026-44</t>
+          <t>13.5 ft</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8901</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Slip K-15</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Hoku Sportfisher</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>720</v>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>DOCARE-OAHU-2026-45</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>2027-06-30</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-202</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Oahu Star</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8902</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-103</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Blue Horizon</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8903</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-204</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Kai Lani</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8904</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-105</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Moana Wave</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8905</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-206</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Pearl</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8906</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-107</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Oahu Star</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8907</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-208</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Blue Horizon</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8908</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-109</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Kai Lani</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8909</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-210</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Moana Wave</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8910</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-111</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #11</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8911</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-212</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #12</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8912</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-113</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #13</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8913</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-214</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #14</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8914</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-115</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #15</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8915</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-216</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #16</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8916</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-117</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #17</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8917</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-218</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #18</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8918</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-119</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #19</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8919</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-220</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #20</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8920</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-121</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #21</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8921</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-222</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #22</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8922</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-123</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #23</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8923</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-224</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #24</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8924</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-125</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #25</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8925</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-226</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #26</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8926</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-127</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #27</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8927</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-228</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #28</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8928</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-129</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #29</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8929</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-230</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #30</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8930</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-131</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #31</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8931</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-232</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #32</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8932</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-133</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #33</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8933</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-234</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #34</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8934</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-135</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #35</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8935</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #35</t>
         </is>
       </c>
     </row>

--- a/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
+++ b/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harbor_Manifest_2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Trail &amp; Documentation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +111,9 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,7 +481,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -2588,4 +2592,4648 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Hash</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Parameter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed SLA Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Clearance Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sign-Off Authority</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:ed7478208c5fdadcd87b1ea8</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 2</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:d8e84c0b4dcd4fb2a01bbe88</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 3</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:73d69ec91833672d76e64fe1</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 4</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:bff8fbf68a1d17f0e2a50cfc</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 5</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:c943f02598ec8ec4bfaef1b1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 6</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:30ae881715b8d94842ec0200</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 7</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:51cb74747fb431e52a5cb065</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 8</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:5e42305829526210c668510f</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 9</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:c0a96d4e9a80298cbdf63e58</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 10</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:06fc76f1e299f2e8efd1fae7</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 11</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:7d741c30c730a437fba7f244</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 12</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:e258862219c9e93cc9ddae8b</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 13</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:8d294a8b8fdf11f4aa262b9c</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 14</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:15ef0b617b35452a11bb610d</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 15</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:3b7b3891ad975f8218e61d0a</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 16</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:0cf2f91f88b6df5e83e8a5fc</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 17</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:66dfdf8668ab0f932baf822c</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 18</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:070cb98454557774ec97911b</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 19</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:8ec969bb0bd7660f58d02603</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 20</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:0bdb553ffdbce98ad6d75fc7</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 21</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:4509e6a295b5c2b63002895a</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 22</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:2886ae8089346d8882c20d3d</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 23</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:7bd4502912e7d9fb1de5c0c0</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 24</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:5a989a8736eefe1b163a596a</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 25</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:3b8aa337d79593093ab84767</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 26</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:ed8b2e941e9c1a9182458f3a</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 27</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:cd5cd5ec3775a4507ff131e9</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 28</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:93e566c40dfa08c183b8d5f9</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 29</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:e580083cc4080d51e80b240e</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 30</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:b870c03f3e144ec44d6ca2c3</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 31</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:95e7f26889054e32bb094b59</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 32</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:e3a0f148bff086ab9521441f</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 33</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:a631916998574997e57ed907</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 34</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:0fe46536f1b25e45c3870e94</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 35</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:8717b3a3d0b65c9ea54d3b96</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 36</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:ade24a917e66c59d40da5e38</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 37</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:691babfa63e9d67deecff4d2</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 38</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:14257bac913bb509919cb965</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 39</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:f0e12373fc1da57a2cbbee27</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 40</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:8eb78187a1964f2443ba8c4f</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 41</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:33e60e28395cab25bd9e170f</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 42</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:30c2373509e673af30ea9a9a</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 43</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:62f0d25afb74fd8af2377326</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 44</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:610aebd055b8018cc27cb700</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 45</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:b88e9144a8d207149de05340</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 46</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:855d3c484aad13b2821caf98</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 47</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:d337a14fb723b2ea3b6540e4</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 48</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:ef42ac888328c7092286f633</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 49</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:4fa69640f46add86ead08e18</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 50</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:57ac1701ae76d68b92400049</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 51</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:a7668a83fe545f0d31fdbd36</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 52</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:d8b9d5ba023e2005bf8db1c2</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 53</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:f0829c65b0ba0e02ba31e572</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 54</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:a8c1d9ee8a030d5c46d4f3cd</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 55</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:181e933db1d2b0a45c884839</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 56</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:279814fc69d31ab12f42c618</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 57</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:cbd11cc59df74959beae9f60</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 58</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:ae8334bf4950f2bf7e2c4828</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 59</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:256733bed437d72c41190a23</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 60</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:fd4c62034eae5238db8f4b58</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 61</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:69eab8c83fe8576f7de74ca9</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 62</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:0485f31196de8b6b89d5831e</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 63</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:fb42dd9da6dc62644c38e608</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 64</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:86dddeaa982b7fcd90d8a5a2</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 65</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:f3b083087da2f9a410f1e1a1</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 66</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:7709717abc5a9bb1c82d4d03</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 67</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:42f6130840da7e8b0747e09a</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 68</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:f742d21efc40560a2adfd178</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 69</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:51e9df009c9ac1664530ed41</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 70</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:bf5c7ff9ec6d3ba2cc6045f3</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 71</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:af46d4dbaeff4d89e90d11d2</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 72</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:0261274e106a0b4a984f159f</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 73</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:9e3a266cbd7aa1fb69e543b9</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 74</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:a7c67329cfb58a0552a08fd0</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 75</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:e1e90701d74a210fe651d726</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 76</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:25e07bd06268214e31b24712</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 77</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:c4c360d02ac0f93bd25dba70</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 78</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:78bc64d76dee24bed17d7aee</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 79</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:2c30e9780d945d3828effa8f</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 80</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:c2c5bfc8248e9bfc9c8fd926</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 81</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:4aad757f1039b6829d88740d</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 82</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:81a00104d83d31e148a591fd</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 83</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:29b30fb7423586cde797f050</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 84</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:71a8ec871ba2866295e0bb6b</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 85</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:ee5ebcf417fc158e3da880a3</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 86</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:25fa49cd6b29ef368527620e</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 87</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:1cf5e0e1d057cbe2ab48dac7</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 88</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:702d3950433b7923ae520672</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 89</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:98d1eceb418ec6e8ec7bf60f</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 90</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:5e56a861fb9d7c57181f3274</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 91</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:38af8c0abb97ed9fdd9707c7</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 92</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:6a92002f4b5cff7b3c883c4d</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 93</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:60f15e32c321ed37757e8d4b</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 94</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:8e4144eaf942dca54f4a0702</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 95</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:dcdfe672ca7ce86783f3b10a</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 96</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:b7b3d5c173fd198b35916fa3</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 97</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:ba908ec5f522ccbfd1f1866a</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 98</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:48c8cd5d87d2b3f7779b3911</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 99</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:fe3113f5ddd96b9ae8383c37</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 100</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:b72b73aacf81daea6d51e074</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 101</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:88f2a341f55fa67f4ed151ec</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 102</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:2fb01f46e76568b67de74414</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 103</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:db97a60615a078357e4b6946</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 104</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:bd9a17caa207a3d017eace7b</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 105</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:dfad98a48a52b631d58f3758</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 106</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:b1491f40ef98184a3137e011</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 107</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:5c4701a972b118a7ecbe3609</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 108</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:bd0602f785f31d85a07e1cdf</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>AUD-REC-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 109</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>SHA256:d71750a244f2012fcf707b84</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
+++ b/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +100,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -108,6 +111,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -480,2112 +486,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Slip ID</t>
+          <t>Berth #</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Harbor Location</t>
+          <t>Vessel Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Berth Berth Tier</t>
+          <t>LOA (ft)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Vessel Name</t>
+          <t>Beam</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length Overall (LOA)</t>
+          <t>Slip Fee / Mo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Beam (ft)</t>
+          <t>Commercial Permit #</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Draft (ft)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Monthly Berth Fee USD</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Electric Metered Fee</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Commercial Landing Permit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Insurance Exp Date</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Owner / Management Entity</t>
+          <t>Expiration Date</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BERTH-KW-101</t>
+          <t>Slip K-14</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Pacific Pearl</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>39 ft</t>
-        </is>
+          <t>Makani Catamaran</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>940</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>13.5 ft</t>
+          <t>DOCARE-OAHU-2026-44</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1805.5</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8901</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2027-002-15</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
+          <t>2027-06-30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-202</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Oahu Star</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>44 ft</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>195</v>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8902</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>2027-003-15</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-103</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Blue Horizon</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>49 ft</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>2050.5</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8903</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>2027-004-15</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-204</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Kai Lani</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>54 ft</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>2173</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>245</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8904</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>2027-005-15</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-105</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Moana Wave</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>59 ft</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>2295.5</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8905</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>2027-006-15</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-206</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Pacific Pearl</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>34 ft</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>1683</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>170</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8906</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>2027-007-15</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-107</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Oahu Star</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>39 ft</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1805.5</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>195</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8907</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>2027-008-15</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-208</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Blue Horizon</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>44 ft</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>220</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8908</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>2027-001-15</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-109</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Kai Lani</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>49 ft</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>2050.5</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8909</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>2027-002-15</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-210</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Moana Wave</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>54 ft</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>2173</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>145</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8910</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>2027-003-15</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-111</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #11</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>59 ft</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>2295.5</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8911</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>2027-004-15</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-212</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #12</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>34 ft</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>1683</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>195</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8912</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>2027-005-15</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>Pacific Oasis Charters LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-113</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #13</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>39 ft</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1805.5</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8913</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>2027-006-15</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #13</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-214</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #14</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>44 ft</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>245</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8914</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>2027-007-15</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-115</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Tier 1 Commercial Slip</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #15</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>49 ft</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>2050.5</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8915</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>2027-008-15</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-216</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #16</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>54 ft</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>2173</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>170</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8916</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>2027-001-15</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #16</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-117</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #17</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>59 ft</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>2295.5</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>195</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8917</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>2027-002-15</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #17</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-218</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #18</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>34 ft</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>1683</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>220</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8918</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>2027-003-15</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-119</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #19</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>39 ft</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1805.5</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8919</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>2027-004-15</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-220</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #20</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>44 ft</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>145</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8920</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>2027-005-15</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-121</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #21</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>49 ft</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2050.5</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8921</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>2027-006-15</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-222</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #22</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>54 ft</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>2173</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>195</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8922</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>2027-007-15</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-123</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #23</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>59 ft</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>2295.5</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8923</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>2027-008-15</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-224</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #24</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>34 ft</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>1683</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>245</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8924</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>2027-001-15</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #24</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-125</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #25</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>39 ft</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1805.5</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8925</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>2027-002-15</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-226</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #26</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>44 ft</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>170</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8926</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>2027-003-15</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #26</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-127</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #27</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>49 ft</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>2050.5</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>195</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8927</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>2027-004-15</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-228</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #28</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>54 ft</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>2173</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>220</v>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8928</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>2027-005-15</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #28</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-129</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #29</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>59 ft</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>2295.5</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>245</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8929</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>2027-006-15</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #29</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-230</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #30</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>34 ft</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>1683</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>145</v>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8930</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>2027-007-15</t>
-        </is>
-      </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #30</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-131</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #31</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>39 ft</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>1805.5</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8931</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>2027-008-15</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #31</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-232</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #32</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>44 ft</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>12.0 ft</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>195</v>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8932</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>2027-001-15</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #32</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-133</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #33</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>49 ft</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>13.5 ft</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>3.5 ft</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>2050.5</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8933</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>2027-002-15</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #33</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>BERTH-AW-234</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Ala Wai Small Boat Harbor</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #34</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>54 ft</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>15.0 ft</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>4.3 ft</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>2173</v>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>245</v>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8934</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>2027-003-15</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #34</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>BERTH-KW-135</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Kewalo Basin Commercial Harbor</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Tier 2 Recreational / Commercial</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Charter Fleet Reserve #35</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>59 ft</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>16.5 ft</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>5.1 ft</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>2295.5</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>HI-DLNR-COMM-8935</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>2027-004-15</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>Hawaii Marine Holding #35</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Slip K-15</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Hoku Sportfisher</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>720</v>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>DOCARE-OAHU-2026-45</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
         </is>
       </c>
     </row>
@@ -2656,4578 +664,4578 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 1</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>SHA256:ed7478208c5fdadcd87b1ea8</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0002</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 2</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>SHA256:d8e84c0b4dcd4fb2a01bbe88</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0003</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 3</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>SHA256:73d69ec91833672d76e64fe1</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0004</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 4</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>SHA256:bff8fbf68a1d17f0e2a50cfc</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0005</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>SHA256:c943f02598ec8ec4bfaef1b1</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0006</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 6</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>SHA256:30ae881715b8d94842ec0200</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0007</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 7</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>SHA256:51cb74747fb431e52a5cb065</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0008</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 8</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>SHA256:5e42305829526210c668510f</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0009</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 9</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>SHA256:c0a96d4e9a80298cbdf63e58</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0010</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 10</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>SHA256:06fc76f1e299f2e8efd1fae7</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0011</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 11</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>SHA256:7d741c30c730a437fba7f244</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0012</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 12</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>SHA256:e258862219c9e93cc9ddae8b</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0013</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 13</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>SHA256:8d294a8b8fdf11f4aa262b9c</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0014</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 14</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>SHA256:15ef0b617b35452a11bb610d</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0015</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 15</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>SHA256:3b7b3891ad975f8218e61d0a</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0016</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 16</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>SHA256:0cf2f91f88b6df5e83e8a5fc</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0017</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 17</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>SHA256:66dfdf8668ab0f932baf822c</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0018</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 18</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>SHA256:070cb98454557774ec97911b</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0019</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 19</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>SHA256:8ec969bb0bd7660f58d02603</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0020</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 20</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>SHA256:0bdb553ffdbce98ad6d75fc7</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0021</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 21</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>SHA256:4509e6a295b5c2b63002895a</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0022</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 22</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>SHA256:2886ae8089346d8882c20d3d</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0023</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 23</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>SHA256:7bd4502912e7d9fb1de5c0c0</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0024</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 24</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>SHA256:5a989a8736eefe1b163a596a</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0025</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 25</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>SHA256:3b8aa337d79593093ab84767</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0026</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 26</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>SHA256:ed8b2e941e9c1a9182458f3a</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0027</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 27</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>SHA256:cd5cd5ec3775a4507ff131e9</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0028</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 28</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>SHA256:93e566c40dfa08c183b8d5f9</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0029</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 29</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>SHA256:e580083cc4080d51e80b240e</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0030</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 30</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>SHA256:b870c03f3e144ec44d6ca2c3</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0031</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 31</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>SHA256:95e7f26889054e32bb094b59</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0032</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 32</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>SHA256:e3a0f148bff086ab9521441f</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0033</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 33</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>SHA256:a631916998574997e57ed907</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0034</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 34</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>SHA256:0fe46536f1b25e45c3870e94</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0035</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 35</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>SHA256:8717b3a3d0b65c9ea54d3b96</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0036</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 36</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>SHA256:ade24a917e66c59d40da5e38</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0037</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 37</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>SHA256:691babfa63e9d67deecff4d2</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0038</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 38</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>SHA256:14257bac913bb509919cb965</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0039</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 39</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>SHA256:f0e12373fc1da57a2cbbee27</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0040</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 40</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>SHA256:8eb78187a1964f2443ba8c4f</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0041</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 41</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>SHA256:33e60e28395cab25bd9e170f</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0042</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 42</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>SHA256:30c2373509e673af30ea9a9a</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0043</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 43</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>SHA256:62f0d25afb74fd8af2377326</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0044</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 44</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>SHA256:610aebd055b8018cc27cb700</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0045</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 45</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>SHA256:b88e9144a8d207149de05340</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0046</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 46</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>SHA256:855d3c484aad13b2821caf98</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0047</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 47</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>SHA256:d337a14fb723b2ea3b6540e4</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0048</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 48</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>SHA256:ef42ac888328c7092286f633</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0049</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 49</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>SHA256:4fa69640f46add86ead08e18</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0050</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 50</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>SHA256:57ac1701ae76d68b92400049</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0051</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 51</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>SHA256:a7668a83fe545f0d31fdbd36</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0052</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 52</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>SHA256:d8b9d5ba023e2005bf8db1c2</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0053</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 53</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>SHA256:f0829c65b0ba0e02ba31e572</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0054</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 54</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>SHA256:a8c1d9ee8a030d5c46d4f3cd</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0055</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 55</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>SHA256:181e933db1d2b0a45c884839</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0056</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 56</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>SHA256:279814fc69d31ab12f42c618</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0057</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 57</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>SHA256:cbd11cc59df74959beae9f60</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0058</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 58</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>SHA256:ae8334bf4950f2bf7e2c4828</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0059</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 59</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>SHA256:256733bed437d72c41190a23</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0060</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 60</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>SHA256:fd4c62034eae5238db8f4b58</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0061</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 61</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>SHA256:69eab8c83fe8576f7de74ca9</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0062</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 62</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>SHA256:0485f31196de8b6b89d5831e</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0063</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 63</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>SHA256:fb42dd9da6dc62644c38e608</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0064</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 64</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>SHA256:86dddeaa982b7fcd90d8a5a2</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0065</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 65</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>SHA256:f3b083087da2f9a410f1e1a1</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0066</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 66</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>SHA256:7709717abc5a9bb1c82d4d03</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0067</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 67</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>SHA256:42f6130840da7e8b0747e09a</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0068</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 68</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>SHA256:f742d21efc40560a2adfd178</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0069</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 69</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>SHA256:51e9df009c9ac1664530ed41</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D70" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0070</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 70</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>SHA256:bf5c7ff9ec6d3ba2cc6045f3</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D71" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0071</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 71</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>SHA256:af46d4dbaeff4d89e90d11d2</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0072</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 72</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>SHA256:0261274e106a0b4a984f159f</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0073</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 73</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>SHA256:9e3a266cbd7aa1fb69e543b9</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0074</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 74</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>SHA256:a7c67329cfb58a0552a08fd0</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0075</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 75</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>SHA256:e1e90701d74a210fe651d726</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0076</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 76</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>SHA256:25e07bd06268214e31b24712</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0077</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 77</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>SHA256:c4c360d02ac0f93bd25dba70</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E78" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0078</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 78</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>SHA256:78bc64d76dee24bed17d7aee</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0079</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 79</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>SHA256:2c30e9780d945d3828effa8f</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E80" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0080</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 80</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>SHA256:c2c5bfc8248e9bfc9c8fd926</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0081</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 81</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>SHA256:4aad757f1039b6829d88740d</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E82" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0082</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 82</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>SHA256:81a00104d83d31e148a591fd</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0083</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 83</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>SHA256:29b30fb7423586cde797f050</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="H84" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0084</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 84</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>SHA256:71a8ec871ba2866295e0bb6b</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D85" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0085</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 85</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>SHA256:ee5ebcf417fc158e3da880a3</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="H86" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0086</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 86</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>SHA256:25fa49cd6b29ef368527620e</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0087</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 87</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>SHA256:1cf5e0e1d057cbe2ab48dac7</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E88" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0088</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 88</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>SHA256:702d3950433b7923ae520672</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr">
+      <c r="H89" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0089</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 89</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>SHA256:98d1eceb418ec6e8ec7bf60f</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="H90" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0090</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 90</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>SHA256:5e56a861fb9d7c57181f3274</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D91" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E91" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="H91" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0091</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 91</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>SHA256:38af8c0abb97ed9fdd9707c7</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E92" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="H92" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0092</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 92</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>SHA256:6a92002f4b5cff7b3c883c4d</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D93" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="H93" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0093</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 93</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>SHA256:60f15e32c321ed37757e8d4b</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="H94" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0094</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 94</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C95" s="10" t="inlineStr">
         <is>
           <t>SHA256:8e4144eaf942dca54f4a0702</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H95" s="8" t="inlineStr">
+      <c r="H95" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0095</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 95</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>SHA256:dcdfe672ca7ce86783f3b10a</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E96" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="H96" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0096</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 96</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>SHA256:b7b3d5c173fd198b35916fa3</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D97" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
+      <c r="E97" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H97" s="8" t="inlineStr">
+      <c r="H97" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0097</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 97</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>SHA256:ba908ec5f522ccbfd1f1866a</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E98" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr">
+      <c r="H98" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0098</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 98</t>
         </is>
       </c>
-      <c r="C99" s="8" t="inlineStr">
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>SHA256:48c8cd5d87d2b3f7779b3911</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E99" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr">
+      <c r="H99" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0099</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 99</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>SHA256:fe3113f5ddd96b9ae8383c37</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="D100" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E100" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr">
+      <c r="H100" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0100</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 100</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>SHA256:b72b73aacf81daea6d51e074</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E101" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="H101" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0101</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 101</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>SHA256:88f2a341f55fa67f4ed151ec</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E102" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr">
+      <c r="H102" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0102</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 102</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>SHA256:2fb01f46e76568b67de74414</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
+      <c r="E103" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0103</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 103</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>SHA256:db97a60615a078357e4b6946</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
+      <c r="E104" s="10" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr">
+      <c r="H104" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0104</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 104</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>SHA256:bd9a17caa207a3d017eace7b</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr">
+      <c r="H105" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0105</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 105</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>SHA256:dfad98a48a52b631d58f3758</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E106" s="10" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G106" s="8" t="inlineStr">
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H106" s="8" t="inlineStr">
+      <c r="H106" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0106</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 106</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>SHA256:b1491f40ef98184a3137e011</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
+      <c r="E107" s="10" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H107" s="8" t="inlineStr">
+      <c r="H107" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0107</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 107</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>SHA256:5c4701a972b118a7ecbe3609</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E108" s="10" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr">
+      <c r="H108" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0108</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 108</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>SHA256:bd0602f785f31d85a07e1cdf</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr">
+      <c r="H109" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>AUD-REC-0109</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 109</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>SHA256:d71750a244f2012fcf707b84</t>
         </is>
       </c>
-      <c r="D110" s="8" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H110" s="8" t="inlineStr">
+      <c r="H110" s="10" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
         </is>

--- a/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
+++ b/public/chat_files/luca_harbor_seasonal_manifest_v2.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,9 +100,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -111,9 +108,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -486,114 +480,2112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Berth #</t>
+          <t>Slip ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Harbor Location</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Berth Berth Tier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Vessel Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LOA (ft)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Beam</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Slip Fee / Mo</t>
+          <t>Length Overall (LOA)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Commercial Permit #</t>
+          <t>Beam (ft)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Expiration Date</t>
+          <t>Draft (ft)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly Berth Fee USD</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Electric Metered Fee</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Commercial Landing Permit</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Insurance Exp Date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Owner / Management Entity</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Slip K-14</t>
+          <t>BERTH-KW-101</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Makani Catamaran</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>940</v>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Pearl</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>DOCARE-OAHU-2026-44</t>
+          <t>13.5 ft</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8901</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Slip K-15</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Hoku Sportfisher</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>720</v>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>DOCARE-OAHU-2026-45</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>2027-06-30</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-202</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Oahu Star</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8902</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-103</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Blue Horizon</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8903</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-204</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Kai Lani</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8904</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-105</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Moana Wave</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8905</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-206</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Pearl</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8906</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-107</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Oahu Star</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8907</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-208</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Blue Horizon</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8908</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-109</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Kai Lani</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8909</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-210</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Moana Wave</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8910</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-111</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #11</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8911</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-212</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #12</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8912</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Pacific Oasis Charters LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-113</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #13</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8913</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-214</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #14</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8914</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-115</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1 Commercial Slip</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #15</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8915</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-216</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #16</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8916</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-117</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #17</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8917</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-218</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #18</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8918</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-119</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #19</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8919</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-220</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #20</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8920</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-121</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #21</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8921</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-222</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #22</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8922</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-123</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #23</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8923</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-224</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #24</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8924</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-125</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #25</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8925</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-226</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #26</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>170</v>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8926</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-127</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #27</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8927</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-228</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #28</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8928</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>2027-005-15</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-129</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #29</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8929</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>2027-006-15</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-230</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #30</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>34 ft</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>1683</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>145</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8930</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>2027-007-15</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-131</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #31</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>39 ft</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1805.5</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8931</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>2027-008-15</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-232</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #32</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>44 ft</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>12.0 ft</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8932</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>2027-001-15</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-133</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #33</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>49 ft</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>13.5 ft</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>3.5 ft</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>2050.5</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8933</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>2027-002-15</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>BERTH-AW-234</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Ala Wai Small Boat Harbor</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #34</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>54 ft</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ft</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>4.3 ft</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>245</v>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8934</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>2027-003-15</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>BERTH-KW-135</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Kewalo Basin Commercial Harbor</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2 Recreational / Commercial</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Charter Fleet Reserve #35</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>59 ft</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>16.5 ft</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>5.1 ft</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>2295.5</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>HI-DLNR-COMM-8935</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>2027-004-15</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Hawaii Marine Holding #35</t>
         </is>
       </c>
     </row>
@@ -664,4578 +2656,4578 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0001</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 1</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>SHA256:ed7478208c5fdadcd87b1ea8</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0002</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 2</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>SHA256:d8e84c0b4dcd4fb2a01bbe88</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0003</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 3</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>SHA256:73d69ec91833672d76e64fe1</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0004</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 4</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>SHA256:bff8fbf68a1d17f0e2a50cfc</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0005</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 5</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SHA256:c943f02598ec8ec4bfaef1b1</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0006</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 6</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>SHA256:30ae881715b8d94842ec0200</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0007</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 7</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>SHA256:51cb74747fb431e52a5cb065</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0008</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 8</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>SHA256:5e42305829526210c668510f</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0009</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 9</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>SHA256:c0a96d4e9a80298cbdf63e58</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0010</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 10</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>SHA256:06fc76f1e299f2e8efd1fae7</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0011</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 11</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>SHA256:7d741c30c730a437fba7f244</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0012</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 12</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>SHA256:e258862219c9e93cc9ddae8b</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0013</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 13</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>SHA256:8d294a8b8fdf11f4aa262b9c</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0014</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 14</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>SHA256:15ef0b617b35452a11bb610d</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0015</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 15</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>SHA256:3b7b3891ad975f8218e61d0a</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0016</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 16</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>SHA256:0cf2f91f88b6df5e83e8a5fc</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0017</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 17</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>SHA256:66dfdf8668ab0f932baf822c</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0018</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 18</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>SHA256:070cb98454557774ec97911b</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0019</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 19</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>SHA256:8ec969bb0bd7660f58d02603</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0020</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 20</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>SHA256:0bdb553ffdbce98ad6d75fc7</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0021</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 21</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>SHA256:4509e6a295b5c2b63002895a</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0022</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 22</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>SHA256:2886ae8089346d8882c20d3d</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0023</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 23</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>SHA256:7bd4502912e7d9fb1de5c0c0</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0024</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 24</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>SHA256:5a989a8736eefe1b163a596a</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0025</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 25</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>SHA256:3b8aa337d79593093ab84767</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0026</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 26</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>SHA256:ed8b2e941e9c1a9182458f3a</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0027</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 27</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>SHA256:cd5cd5ec3775a4507ff131e9</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0028</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 28</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>SHA256:93e566c40dfa08c183b8d5f9</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0029</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 29</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>SHA256:e580083cc4080d51e80b240e</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0030</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 30</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>SHA256:b870c03f3e144ec44d6ca2c3</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0031</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 31</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>SHA256:95e7f26889054e32bb094b59</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0032</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 32</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>SHA256:e3a0f148bff086ab9521441f</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0033</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 33</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>SHA256:a631916998574997e57ed907</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0034</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 34</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>SHA256:0fe46536f1b25e45c3870e94</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0035</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 35</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>SHA256:8717b3a3d0b65c9ea54d3b96</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0036</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 36</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>SHA256:ade24a917e66c59d40da5e38</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0037</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 37</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>SHA256:691babfa63e9d67deecff4d2</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0038</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 38</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>SHA256:14257bac913bb509919cb965</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0039</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 39</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>SHA256:f0e12373fc1da57a2cbbee27</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0040</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 40</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>SHA256:8eb78187a1964f2443ba8c4f</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0041</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 41</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>SHA256:33e60e28395cab25bd9e170f</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0042</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 42</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>SHA256:30c2373509e673af30ea9a9a</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0043</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 43</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>SHA256:62f0d25afb74fd8af2377326</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0044</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 44</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>SHA256:610aebd055b8018cc27cb700</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0045</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 45</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>SHA256:b88e9144a8d207149de05340</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0046</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 46</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>SHA256:855d3c484aad13b2821caf98</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0047</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 47</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>SHA256:d337a14fb723b2ea3b6540e4</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0048</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 48</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>SHA256:ef42ac888328c7092286f633</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0049</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 49</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>SHA256:4fa69640f46add86ead08e18</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0050</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 50</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>SHA256:57ac1701ae76d68b92400049</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0051</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 51</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHA256:a7668a83fe545f0d31fdbd36</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0052</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 52</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>SHA256:d8b9d5ba023e2005bf8db1c2</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0053</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 53</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>SHA256:f0829c65b0ba0e02ba31e572</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0054</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 54</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>SHA256:a8c1d9ee8a030d5c46d4f3cd</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0055</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 55</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>SHA256:181e933db1d2b0a45c884839</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0056</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 56</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>SHA256:279814fc69d31ab12f42c618</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0057</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 57</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>SHA256:cbd11cc59df74959beae9f60</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0058</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 58</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>SHA256:ae8334bf4950f2bf7e2c4828</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0059</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 59</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>SHA256:256733bed437d72c41190a23</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0060</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 60</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>SHA256:fd4c62034eae5238db8f4b58</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0061</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 61</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>SHA256:69eab8c83fe8576f7de74ca9</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0062</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 62</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>SHA256:0485f31196de8b6b89d5831e</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0063</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 63</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>SHA256:fb42dd9da6dc62644c38e608</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0064</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 64</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>SHA256:86dddeaa982b7fcd90d8a5a2</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0065</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 65</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>SHA256:f3b083087da2f9a410f1e1a1</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0066</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 66</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>SHA256:7709717abc5a9bb1c82d4d03</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0067</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 67</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>SHA256:42f6130840da7e8b0747e09a</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0068</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 68</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>SHA256:f742d21efc40560a2adfd178</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0069</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 69</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>SHA256:51e9df009c9ac1664530ed41</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0070</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 70</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>SHA256:bf5c7ff9ec6d3ba2cc6045f3</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G71" s="10" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0071</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 71</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>SHA256:af46d4dbaeff4d89e90d11d2</t>
         </is>
       </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0072</t>
         </is>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 72</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>SHA256:0261274e106a0b4a984f159f</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0073</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 73</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>SHA256:9e3a266cbd7aa1fb69e543b9</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0074</t>
         </is>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 74</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>SHA256:a7c67329cfb58a0552a08fd0</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0075</t>
         </is>
       </c>
-      <c r="B76" s="10" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 75</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>SHA256:e1e90701d74a210fe651d726</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0076</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 76</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>SHA256:25e07bd06268214e31b24712</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0077</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 77</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>SHA256:c4c360d02ac0f93bd25dba70</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H78" s="10" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0078</t>
         </is>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 78</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>SHA256:78bc64d76dee24bed17d7aee</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0079</t>
         </is>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 79</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>SHA256:2c30e9780d945d3828effa8f</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0080</t>
         </is>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 80</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>SHA256:c2c5bfc8248e9bfc9c8fd926</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H81" s="10" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0081</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 81</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>SHA256:4aad757f1039b6829d88740d</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H82" s="10" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0082</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 82</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>SHA256:81a00104d83d31e148a591fd</t>
         </is>
       </c>
-      <c r="D83" s="10" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0083</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 83</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>SHA256:29b30fb7423586cde797f050</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0084</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 84</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>SHA256:71a8ec871ba2866295e0bb6b</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0085</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 85</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>SHA256:ee5ebcf417fc158e3da880a3</t>
         </is>
       </c>
-      <c r="D86" s="10" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0086</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 86</t>
         </is>
       </c>
-      <c r="C87" s="10" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>SHA256:25fa49cd6b29ef368527620e</t>
         </is>
       </c>
-      <c r="D87" s="10" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0087</t>
         </is>
       </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 87</t>
         </is>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>SHA256:1cf5e0e1d057cbe2ab48dac7</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0088</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 88</t>
         </is>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>SHA256:702d3950433b7923ae520672</t>
         </is>
       </c>
-      <c r="D89" s="10" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H89" s="10" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0089</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 89</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>SHA256:98d1eceb418ec6e8ec7bf60f</t>
         </is>
       </c>
-      <c r="D90" s="10" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H90" s="10" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0090</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 90</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>SHA256:5e56a861fb9d7c57181f3274</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E91" s="10" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H91" s="10" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0091</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 91</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>SHA256:38af8c0abb97ed9fdd9707c7</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0092</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 92</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr">
         <is>
           <t>SHA256:6a92002f4b5cff7b3c883c4d</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H93" s="10" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0093</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 93</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>SHA256:60f15e32c321ed37757e8d4b</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0094</t>
         </is>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 94</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>SHA256:8e4144eaf942dca54f4a0702</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G95" s="10" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0095</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 95</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>SHA256:dcdfe672ca7ce86783f3b10a</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0096</t>
         </is>
       </c>
-      <c r="B97" s="10" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 96</t>
         </is>
       </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>SHA256:b7b3d5c173fd198b35916fa3</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E97" s="10" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G97" s="10" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0097</t>
         </is>
       </c>
-      <c r="B98" s="10" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 97</t>
         </is>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>SHA256:ba908ec5f522ccbfd1f1866a</t>
         </is>
       </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E98" s="10" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G98" s="10" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H98" s="10" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0098</t>
         </is>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 98</t>
         </is>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>SHA256:48c8cd5d87d2b3f7779b3911</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E99" s="10" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0099</t>
         </is>
       </c>
-      <c r="B100" s="10" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 99</t>
         </is>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>SHA256:fe3113f5ddd96b9ae8383c37</t>
         </is>
       </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E100" s="10" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G100" s="10" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0100</t>
         </is>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 100</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>SHA256:b72b73aacf81daea6d51e074</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0101</t>
         </is>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 101</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>SHA256:88f2a341f55fa67f4ed151ec</t>
         </is>
       </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E102" s="10" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G102" s="10" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0102</t>
         </is>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 102</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>SHA256:2fb01f46e76568b67de74414</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E103" s="10" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G103" s="10" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H103" s="10" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0103</t>
         </is>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 103</t>
         </is>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>SHA256:db97a60615a078357e4b6946</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>99.50%</t>
         </is>
       </c>
-      <c r="F104" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G104" s="10" t="inlineStr">
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H104" s="10" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0104</t>
         </is>
       </c>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 104</t>
         </is>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>SHA256:bd9a17caa207a3d017eace7b</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>99.70%</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G105" s="10" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0105</t>
         </is>
       </c>
-      <c r="B106" s="10" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 105</t>
         </is>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>SHA256:dfad98a48a52b631d58f3758</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D106" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E106" s="10" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>98.50%</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G106" s="10" t="inlineStr">
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #100</t>
         </is>
       </c>
-      <c r="H106" s="10" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0106</t>
         </is>
       </c>
-      <c r="B107" s="10" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 106</t>
         </is>
       </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>SHA256:b1491f40ef98184a3137e011</t>
         </is>
       </c>
-      <c r="D107" s="10" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>98.70%</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G107" s="10" t="inlineStr">
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #101</t>
         </is>
       </c>
-      <c r="H107" s="10" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0107</t>
         </is>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 107</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>SHA256:5c4701a972b118a7ecbe3609</t>
         </is>
       </c>
-      <c r="D108" s="10" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E108" s="10" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>98.90%</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G108" s="10" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #102</t>
         </is>
       </c>
-      <c r="H108" s="10" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0108</t>
         </is>
       </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 108</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>SHA256:bd0602f785f31d85a07e1cdf</t>
         </is>
       </c>
-      <c r="D109" s="10" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>99.10%</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #103</t>
         </is>
       </c>
-      <c r="H109" s="10" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>AUD-REC-0109</t>
         </is>
       </c>
-      <c r="B110" s="10" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>Enterprise Client Operational Node 109</t>
         </is>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>SHA256:d71750a244f2012fcf707b84</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D110" s="8" t="inlineStr">
         <is>
           <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
         </is>
       </c>
-      <c r="E110" s="10" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>99.30%</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
-        <is>
-          <t>CLEARED_AND_ARCHIVED</t>
-        </is>
-      </c>
-      <c r="G110" s="10" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>Senior Assurance Officer #104</t>
         </is>
       </c>
-      <c r="H110" s="10" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
         </is>
